--- a/templates_excel/工作日历.xlsx
+++ b/templates_excel/工作日历.xlsx
@@ -16,14 +16,19 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -46,8 +51,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,80 +436,3088 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>类型</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>可用工时</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>效率</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>允许普通件</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>允许急件</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>2026-01-21</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>工作日</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>是</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>是</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>示例</t>
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="6" t="n"/>
+      <c r="C3" s="7" t="n"/>
+      <c r="D3" s="7" t="n"/>
+      <c r="G3" s="8" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="n"/>
+      <c r="C4" s="7" t="n"/>
+      <c r="D4" s="7" t="n"/>
+      <c r="G4" s="8" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="n"/>
+      <c r="C5" s="7" t="n"/>
+      <c r="D5" s="7" t="n"/>
+      <c r="G5" s="8" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="n"/>
+      <c r="C6" s="7" t="n"/>
+      <c r="D6" s="7" t="n"/>
+      <c r="G6" s="8" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n"/>
+      <c r="C7" s="7" t="n"/>
+      <c r="D7" s="7" t="n"/>
+      <c r="G7" s="8" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n"/>
+      <c r="C8" s="7" t="n"/>
+      <c r="D8" s="7" t="n"/>
+      <c r="G8" s="8" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n"/>
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="7" t="n"/>
+      <c r="G9" s="8" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n"/>
+      <c r="C10" s="7" t="n"/>
+      <c r="D10" s="7" t="n"/>
+      <c r="G10" s="8" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n"/>
+      <c r="C11" s="7" t="n"/>
+      <c r="D11" s="7" t="n"/>
+      <c r="G11" s="8" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n"/>
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="7" t="n"/>
+      <c r="G12" s="8" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n"/>
+      <c r="C13" s="7" t="n"/>
+      <c r="D13" s="7" t="n"/>
+      <c r="G13" s="8" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="n"/>
+      <c r="C14" s="7" t="n"/>
+      <c r="D14" s="7" t="n"/>
+      <c r="G14" s="8" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n"/>
+      <c r="C15" s="7" t="n"/>
+      <c r="D15" s="7" t="n"/>
+      <c r="G15" s="8" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n"/>
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="7" t="n"/>
+      <c r="G16" s="8" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n"/>
+      <c r="C17" s="7" t="n"/>
+      <c r="D17" s="7" t="n"/>
+      <c r="G17" s="8" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="n"/>
+      <c r="C18" s="7" t="n"/>
+      <c r="D18" s="7" t="n"/>
+      <c r="G18" s="8" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="n"/>
+      <c r="C19" s="7" t="n"/>
+      <c r="D19" s="7" t="n"/>
+      <c r="G19" s="8" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="n"/>
+      <c r="C20" s="7" t="n"/>
+      <c r="D20" s="7" t="n"/>
+      <c r="G20" s="8" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="n"/>
+      <c r="C21" s="7" t="n"/>
+      <c r="D21" s="7" t="n"/>
+      <c r="G21" s="8" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="n"/>
+      <c r="C22" s="7" t="n"/>
+      <c r="D22" s="7" t="n"/>
+      <c r="G22" s="8" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="n"/>
+      <c r="C23" s="7" t="n"/>
+      <c r="D23" s="7" t="n"/>
+      <c r="G23" s="8" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="n"/>
+      <c r="C24" s="7" t="n"/>
+      <c r="D24" s="7" t="n"/>
+      <c r="G24" s="8" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="n"/>
+      <c r="C25" s="7" t="n"/>
+      <c r="D25" s="7" t="n"/>
+      <c r="G25" s="8" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="n"/>
+      <c r="C26" s="7" t="n"/>
+      <c r="D26" s="7" t="n"/>
+      <c r="G26" s="8" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="n"/>
+      <c r="C27" s="7" t="n"/>
+      <c r="D27" s="7" t="n"/>
+      <c r="G27" s="8" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="n"/>
+      <c r="C28" s="7" t="n"/>
+      <c r="D28" s="7" t="n"/>
+      <c r="G28" s="8" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="n"/>
+      <c r="C29" s="7" t="n"/>
+      <c r="D29" s="7" t="n"/>
+      <c r="G29" s="8" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="n"/>
+      <c r="C30" s="7" t="n"/>
+      <c r="D30" s="7" t="n"/>
+      <c r="G30" s="8" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="n"/>
+      <c r="C31" s="7" t="n"/>
+      <c r="D31" s="7" t="n"/>
+      <c r="G31" s="8" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="n"/>
+      <c r="C32" s="7" t="n"/>
+      <c r="D32" s="7" t="n"/>
+      <c r="G32" s="8" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="n"/>
+      <c r="C33" s="7" t="n"/>
+      <c r="D33" s="7" t="n"/>
+      <c r="G33" s="8" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="n"/>
+      <c r="C34" s="7" t="n"/>
+      <c r="D34" s="7" t="n"/>
+      <c r="G34" s="8" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="n"/>
+      <c r="C35" s="7" t="n"/>
+      <c r="D35" s="7" t="n"/>
+      <c r="G35" s="8" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="n"/>
+      <c r="C36" s="7" t="n"/>
+      <c r="D36" s="7" t="n"/>
+      <c r="G36" s="8" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="n"/>
+      <c r="C37" s="7" t="n"/>
+      <c r="D37" s="7" t="n"/>
+      <c r="G37" s="8" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="n"/>
+      <c r="C38" s="7" t="n"/>
+      <c r="D38" s="7" t="n"/>
+      <c r="G38" s="8" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="n"/>
+      <c r="C39" s="7" t="n"/>
+      <c r="D39" s="7" t="n"/>
+      <c r="G39" s="8" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="n"/>
+      <c r="C40" s="7" t="n"/>
+      <c r="D40" s="7" t="n"/>
+      <c r="G40" s="8" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="n"/>
+      <c r="C41" s="7" t="n"/>
+      <c r="D41" s="7" t="n"/>
+      <c r="G41" s="8" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="n"/>
+      <c r="C42" s="7" t="n"/>
+      <c r="D42" s="7" t="n"/>
+      <c r="G42" s="8" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="n"/>
+      <c r="C43" s="7" t="n"/>
+      <c r="D43" s="7" t="n"/>
+      <c r="G43" s="8" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="n"/>
+      <c r="C44" s="7" t="n"/>
+      <c r="D44" s="7" t="n"/>
+      <c r="G44" s="8" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="n"/>
+      <c r="C45" s="7" t="n"/>
+      <c r="D45" s="7" t="n"/>
+      <c r="G45" s="8" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="n"/>
+      <c r="C46" s="7" t="n"/>
+      <c r="D46" s="7" t="n"/>
+      <c r="G46" s="8" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="n"/>
+      <c r="C47" s="7" t="n"/>
+      <c r="D47" s="7" t="n"/>
+      <c r="G47" s="8" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="n"/>
+      <c r="C48" s="7" t="n"/>
+      <c r="D48" s="7" t="n"/>
+      <c r="G48" s="8" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="n"/>
+      <c r="C49" s="7" t="n"/>
+      <c r="D49" s="7" t="n"/>
+      <c r="G49" s="8" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="n"/>
+      <c r="C50" s="7" t="n"/>
+      <c r="D50" s="7" t="n"/>
+      <c r="G50" s="8" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="n"/>
+      <c r="C51" s="7" t="n"/>
+      <c r="D51" s="7" t="n"/>
+      <c r="G51" s="8" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="n"/>
+      <c r="C52" s="7" t="n"/>
+      <c r="D52" s="7" t="n"/>
+      <c r="G52" s="8" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="n"/>
+      <c r="C53" s="7" t="n"/>
+      <c r="D53" s="7" t="n"/>
+      <c r="G53" s="8" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="n"/>
+      <c r="C54" s="7" t="n"/>
+      <c r="D54" s="7" t="n"/>
+      <c r="G54" s="8" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="n"/>
+      <c r="C55" s="7" t="n"/>
+      <c r="D55" s="7" t="n"/>
+      <c r="G55" s="8" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="n"/>
+      <c r="C56" s="7" t="n"/>
+      <c r="D56" s="7" t="n"/>
+      <c r="G56" s="8" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="n"/>
+      <c r="C57" s="7" t="n"/>
+      <c r="D57" s="7" t="n"/>
+      <c r="G57" s="8" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="n"/>
+      <c r="C58" s="7" t="n"/>
+      <c r="D58" s="7" t="n"/>
+      <c r="G58" s="8" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="n"/>
+      <c r="C59" s="7" t="n"/>
+      <c r="D59" s="7" t="n"/>
+      <c r="G59" s="8" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="n"/>
+      <c r="C60" s="7" t="n"/>
+      <c r="D60" s="7" t="n"/>
+      <c r="G60" s="8" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="n"/>
+      <c r="C61" s="7" t="n"/>
+      <c r="D61" s="7" t="n"/>
+      <c r="G61" s="8" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="n"/>
+      <c r="C62" s="7" t="n"/>
+      <c r="D62" s="7" t="n"/>
+      <c r="G62" s="8" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="n"/>
+      <c r="C63" s="7" t="n"/>
+      <c r="D63" s="7" t="n"/>
+      <c r="G63" s="8" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="n"/>
+      <c r="C64" s="7" t="n"/>
+      <c r="D64" s="7" t="n"/>
+      <c r="G64" s="8" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="n"/>
+      <c r="C65" s="7" t="n"/>
+      <c r="D65" s="7" t="n"/>
+      <c r="G65" s="8" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="n"/>
+      <c r="C66" s="7" t="n"/>
+      <c r="D66" s="7" t="n"/>
+      <c r="G66" s="8" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="n"/>
+      <c r="C67" s="7" t="n"/>
+      <c r="D67" s="7" t="n"/>
+      <c r="G67" s="8" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="n"/>
+      <c r="C68" s="7" t="n"/>
+      <c r="D68" s="7" t="n"/>
+      <c r="G68" s="8" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="n"/>
+      <c r="C69" s="7" t="n"/>
+      <c r="D69" s="7" t="n"/>
+      <c r="G69" s="8" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="n"/>
+      <c r="C70" s="7" t="n"/>
+      <c r="D70" s="7" t="n"/>
+      <c r="G70" s="8" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="n"/>
+      <c r="C71" s="7" t="n"/>
+      <c r="D71" s="7" t="n"/>
+      <c r="G71" s="8" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="n"/>
+      <c r="C72" s="7" t="n"/>
+      <c r="D72" s="7" t="n"/>
+      <c r="G72" s="8" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="n"/>
+      <c r="C73" s="7" t="n"/>
+      <c r="D73" s="7" t="n"/>
+      <c r="G73" s="8" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="n"/>
+      <c r="C74" s="7" t="n"/>
+      <c r="D74" s="7" t="n"/>
+      <c r="G74" s="8" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="n"/>
+      <c r="C75" s="7" t="n"/>
+      <c r="D75" s="7" t="n"/>
+      <c r="G75" s="8" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="n"/>
+      <c r="C76" s="7" t="n"/>
+      <c r="D76" s="7" t="n"/>
+      <c r="G76" s="8" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="n"/>
+      <c r="C77" s="7" t="n"/>
+      <c r="D77" s="7" t="n"/>
+      <c r="G77" s="8" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="n"/>
+      <c r="C78" s="7" t="n"/>
+      <c r="D78" s="7" t="n"/>
+      <c r="G78" s="8" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="n"/>
+      <c r="C79" s="7" t="n"/>
+      <c r="D79" s="7" t="n"/>
+      <c r="G79" s="8" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="n"/>
+      <c r="C80" s="7" t="n"/>
+      <c r="D80" s="7" t="n"/>
+      <c r="G80" s="8" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="n"/>
+      <c r="C81" s="7" t="n"/>
+      <c r="D81" s="7" t="n"/>
+      <c r="G81" s="8" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="n"/>
+      <c r="C82" s="7" t="n"/>
+      <c r="D82" s="7" t="n"/>
+      <c r="G82" s="8" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="n"/>
+      <c r="C83" s="7" t="n"/>
+      <c r="D83" s="7" t="n"/>
+      <c r="G83" s="8" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="n"/>
+      <c r="C84" s="7" t="n"/>
+      <c r="D84" s="7" t="n"/>
+      <c r="G84" s="8" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="n"/>
+      <c r="C85" s="7" t="n"/>
+      <c r="D85" s="7" t="n"/>
+      <c r="G85" s="8" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="n"/>
+      <c r="C86" s="7" t="n"/>
+      <c r="D86" s="7" t="n"/>
+      <c r="G86" s="8" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="n"/>
+      <c r="C87" s="7" t="n"/>
+      <c r="D87" s="7" t="n"/>
+      <c r="G87" s="8" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="n"/>
+      <c r="C88" s="7" t="n"/>
+      <c r="D88" s="7" t="n"/>
+      <c r="G88" s="8" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="n"/>
+      <c r="C89" s="7" t="n"/>
+      <c r="D89" s="7" t="n"/>
+      <c r="G89" s="8" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="n"/>
+      <c r="C90" s="7" t="n"/>
+      <c r="D90" s="7" t="n"/>
+      <c r="G90" s="8" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="n"/>
+      <c r="C91" s="7" t="n"/>
+      <c r="D91" s="7" t="n"/>
+      <c r="G91" s="8" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="n"/>
+      <c r="C92" s="7" t="n"/>
+      <c r="D92" s="7" t="n"/>
+      <c r="G92" s="8" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="n"/>
+      <c r="C93" s="7" t="n"/>
+      <c r="D93" s="7" t="n"/>
+      <c r="G93" s="8" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="n"/>
+      <c r="C94" s="7" t="n"/>
+      <c r="D94" s="7" t="n"/>
+      <c r="G94" s="8" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="n"/>
+      <c r="C95" s="7" t="n"/>
+      <c r="D95" s="7" t="n"/>
+      <c r="G95" s="8" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="6" t="n"/>
+      <c r="C96" s="7" t="n"/>
+      <c r="D96" s="7" t="n"/>
+      <c r="G96" s="8" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="n"/>
+      <c r="C97" s="7" t="n"/>
+      <c r="D97" s="7" t="n"/>
+      <c r="G97" s="8" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="6" t="n"/>
+      <c r="C98" s="7" t="n"/>
+      <c r="D98" s="7" t="n"/>
+      <c r="G98" s="8" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="6" t="n"/>
+      <c r="C99" s="7" t="n"/>
+      <c r="D99" s="7" t="n"/>
+      <c r="G99" s="8" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="6" t="n"/>
+      <c r="C100" s="7" t="n"/>
+      <c r="D100" s="7" t="n"/>
+      <c r="G100" s="8" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="6" t="n"/>
+      <c r="C101" s="7" t="n"/>
+      <c r="D101" s="7" t="n"/>
+      <c r="G101" s="8" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="6" t="n"/>
+      <c r="C102" s="7" t="n"/>
+      <c r="D102" s="7" t="n"/>
+      <c r="G102" s="8" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="6" t="n"/>
+      <c r="C103" s="7" t="n"/>
+      <c r="D103" s="7" t="n"/>
+      <c r="G103" s="8" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="6" t="n"/>
+      <c r="C104" s="7" t="n"/>
+      <c r="D104" s="7" t="n"/>
+      <c r="G104" s="8" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="6" t="n"/>
+      <c r="C105" s="7" t="n"/>
+      <c r="D105" s="7" t="n"/>
+      <c r="G105" s="8" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="6" t="n"/>
+      <c r="C106" s="7" t="n"/>
+      <c r="D106" s="7" t="n"/>
+      <c r="G106" s="8" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="6" t="n"/>
+      <c r="C107" s="7" t="n"/>
+      <c r="D107" s="7" t="n"/>
+      <c r="G107" s="8" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="6" t="n"/>
+      <c r="C108" s="7" t="n"/>
+      <c r="D108" s="7" t="n"/>
+      <c r="G108" s="8" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="6" t="n"/>
+      <c r="C109" s="7" t="n"/>
+      <c r="D109" s="7" t="n"/>
+      <c r="G109" s="8" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="6" t="n"/>
+      <c r="C110" s="7" t="n"/>
+      <c r="D110" s="7" t="n"/>
+      <c r="G110" s="8" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="6" t="n"/>
+      <c r="C111" s="7" t="n"/>
+      <c r="D111" s="7" t="n"/>
+      <c r="G111" s="8" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="6" t="n"/>
+      <c r="C112" s="7" t="n"/>
+      <c r="D112" s="7" t="n"/>
+      <c r="G112" s="8" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="6" t="n"/>
+      <c r="C113" s="7" t="n"/>
+      <c r="D113" s="7" t="n"/>
+      <c r="G113" s="8" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="6" t="n"/>
+      <c r="C114" s="7" t="n"/>
+      <c r="D114" s="7" t="n"/>
+      <c r="G114" s="8" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="6" t="n"/>
+      <c r="C115" s="7" t="n"/>
+      <c r="D115" s="7" t="n"/>
+      <c r="G115" s="8" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="6" t="n"/>
+      <c r="C116" s="7" t="n"/>
+      <c r="D116" s="7" t="n"/>
+      <c r="G116" s="8" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="6" t="n"/>
+      <c r="C117" s="7" t="n"/>
+      <c r="D117" s="7" t="n"/>
+      <c r="G117" s="8" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="6" t="n"/>
+      <c r="C118" s="7" t="n"/>
+      <c r="D118" s="7" t="n"/>
+      <c r="G118" s="8" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="6" t="n"/>
+      <c r="C119" s="7" t="n"/>
+      <c r="D119" s="7" t="n"/>
+      <c r="G119" s="8" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="6" t="n"/>
+      <c r="C120" s="7" t="n"/>
+      <c r="D120" s="7" t="n"/>
+      <c r="G120" s="8" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="6" t="n"/>
+      <c r="C121" s="7" t="n"/>
+      <c r="D121" s="7" t="n"/>
+      <c r="G121" s="8" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="6" t="n"/>
+      <c r="C122" s="7" t="n"/>
+      <c r="D122" s="7" t="n"/>
+      <c r="G122" s="8" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="6" t="n"/>
+      <c r="C123" s="7" t="n"/>
+      <c r="D123" s="7" t="n"/>
+      <c r="G123" s="8" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="6" t="n"/>
+      <c r="C124" s="7" t="n"/>
+      <c r="D124" s="7" t="n"/>
+      <c r="G124" s="8" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="6" t="n"/>
+      <c r="C125" s="7" t="n"/>
+      <c r="D125" s="7" t="n"/>
+      <c r="G125" s="8" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="6" t="n"/>
+      <c r="C126" s="7" t="n"/>
+      <c r="D126" s="7" t="n"/>
+      <c r="G126" s="8" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="6" t="n"/>
+      <c r="C127" s="7" t="n"/>
+      <c r="D127" s="7" t="n"/>
+      <c r="G127" s="8" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="6" t="n"/>
+      <c r="C128" s="7" t="n"/>
+      <c r="D128" s="7" t="n"/>
+      <c r="G128" s="8" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="6" t="n"/>
+      <c r="C129" s="7" t="n"/>
+      <c r="D129" s="7" t="n"/>
+      <c r="G129" s="8" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="6" t="n"/>
+      <c r="C130" s="7" t="n"/>
+      <c r="D130" s="7" t="n"/>
+      <c r="G130" s="8" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="6" t="n"/>
+      <c r="C131" s="7" t="n"/>
+      <c r="D131" s="7" t="n"/>
+      <c r="G131" s="8" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="6" t="n"/>
+      <c r="C132" s="7" t="n"/>
+      <c r="D132" s="7" t="n"/>
+      <c r="G132" s="8" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="6" t="n"/>
+      <c r="C133" s="7" t="n"/>
+      <c r="D133" s="7" t="n"/>
+      <c r="G133" s="8" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="6" t="n"/>
+      <c r="C134" s="7" t="n"/>
+      <c r="D134" s="7" t="n"/>
+      <c r="G134" s="8" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="6" t="n"/>
+      <c r="C135" s="7" t="n"/>
+      <c r="D135" s="7" t="n"/>
+      <c r="G135" s="8" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="6" t="n"/>
+      <c r="C136" s="7" t="n"/>
+      <c r="D136" s="7" t="n"/>
+      <c r="G136" s="8" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="6" t="n"/>
+      <c r="C137" s="7" t="n"/>
+      <c r="D137" s="7" t="n"/>
+      <c r="G137" s="8" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="6" t="n"/>
+      <c r="C138" s="7" t="n"/>
+      <c r="D138" s="7" t="n"/>
+      <c r="G138" s="8" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="6" t="n"/>
+      <c r="C139" s="7" t="n"/>
+      <c r="D139" s="7" t="n"/>
+      <c r="G139" s="8" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="6" t="n"/>
+      <c r="C140" s="7" t="n"/>
+      <c r="D140" s="7" t="n"/>
+      <c r="G140" s="8" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="6" t="n"/>
+      <c r="C141" s="7" t="n"/>
+      <c r="D141" s="7" t="n"/>
+      <c r="G141" s="8" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="6" t="n"/>
+      <c r="C142" s="7" t="n"/>
+      <c r="D142" s="7" t="n"/>
+      <c r="G142" s="8" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="6" t="n"/>
+      <c r="C143" s="7" t="n"/>
+      <c r="D143" s="7" t="n"/>
+      <c r="G143" s="8" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="6" t="n"/>
+      <c r="C144" s="7" t="n"/>
+      <c r="D144" s="7" t="n"/>
+      <c r="G144" s="8" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="6" t="n"/>
+      <c r="C145" s="7" t="n"/>
+      <c r="D145" s="7" t="n"/>
+      <c r="G145" s="8" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="6" t="n"/>
+      <c r="C146" s="7" t="n"/>
+      <c r="D146" s="7" t="n"/>
+      <c r="G146" s="8" t="n"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="6" t="n"/>
+      <c r="C147" s="7" t="n"/>
+      <c r="D147" s="7" t="n"/>
+      <c r="G147" s="8" t="n"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="6" t="n"/>
+      <c r="C148" s="7" t="n"/>
+      <c r="D148" s="7" t="n"/>
+      <c r="G148" s="8" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="6" t="n"/>
+      <c r="C149" s="7" t="n"/>
+      <c r="D149" s="7" t="n"/>
+      <c r="G149" s="8" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="6" t="n"/>
+      <c r="C150" s="7" t="n"/>
+      <c r="D150" s="7" t="n"/>
+      <c r="G150" s="8" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="6" t="n"/>
+      <c r="C151" s="7" t="n"/>
+      <c r="D151" s="7" t="n"/>
+      <c r="G151" s="8" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="6" t="n"/>
+      <c r="C152" s="7" t="n"/>
+      <c r="D152" s="7" t="n"/>
+      <c r="G152" s="8" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="6" t="n"/>
+      <c r="C153" s="7" t="n"/>
+      <c r="D153" s="7" t="n"/>
+      <c r="G153" s="8" t="n"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="6" t="n"/>
+      <c r="C154" s="7" t="n"/>
+      <c r="D154" s="7" t="n"/>
+      <c r="G154" s="8" t="n"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="6" t="n"/>
+      <c r="C155" s="7" t="n"/>
+      <c r="D155" s="7" t="n"/>
+      <c r="G155" s="8" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="6" t="n"/>
+      <c r="C156" s="7" t="n"/>
+      <c r="D156" s="7" t="n"/>
+      <c r="G156" s="8" t="n"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="6" t="n"/>
+      <c r="C157" s="7" t="n"/>
+      <c r="D157" s="7" t="n"/>
+      <c r="G157" s="8" t="n"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="6" t="n"/>
+      <c r="C158" s="7" t="n"/>
+      <c r="D158" s="7" t="n"/>
+      <c r="G158" s="8" t="n"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="6" t="n"/>
+      <c r="C159" s="7" t="n"/>
+      <c r="D159" s="7" t="n"/>
+      <c r="G159" s="8" t="n"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="6" t="n"/>
+      <c r="C160" s="7" t="n"/>
+      <c r="D160" s="7" t="n"/>
+      <c r="G160" s="8" t="n"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="6" t="n"/>
+      <c r="C161" s="7" t="n"/>
+      <c r="D161" s="7" t="n"/>
+      <c r="G161" s="8" t="n"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="6" t="n"/>
+      <c r="C162" s="7" t="n"/>
+      <c r="D162" s="7" t="n"/>
+      <c r="G162" s="8" t="n"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="6" t="n"/>
+      <c r="C163" s="7" t="n"/>
+      <c r="D163" s="7" t="n"/>
+      <c r="G163" s="8" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="6" t="n"/>
+      <c r="C164" s="7" t="n"/>
+      <c r="D164" s="7" t="n"/>
+      <c r="G164" s="8" t="n"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="6" t="n"/>
+      <c r="C165" s="7" t="n"/>
+      <c r="D165" s="7" t="n"/>
+      <c r="G165" s="8" t="n"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="6" t="n"/>
+      <c r="C166" s="7" t="n"/>
+      <c r="D166" s="7" t="n"/>
+      <c r="G166" s="8" t="n"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="6" t="n"/>
+      <c r="C167" s="7" t="n"/>
+      <c r="D167" s="7" t="n"/>
+      <c r="G167" s="8" t="n"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="6" t="n"/>
+      <c r="C168" s="7" t="n"/>
+      <c r="D168" s="7" t="n"/>
+      <c r="G168" s="8" t="n"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="6" t="n"/>
+      <c r="C169" s="7" t="n"/>
+      <c r="D169" s="7" t="n"/>
+      <c r="G169" s="8" t="n"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="6" t="n"/>
+      <c r="C170" s="7" t="n"/>
+      <c r="D170" s="7" t="n"/>
+      <c r="G170" s="8" t="n"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="6" t="n"/>
+      <c r="C171" s="7" t="n"/>
+      <c r="D171" s="7" t="n"/>
+      <c r="G171" s="8" t="n"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="6" t="n"/>
+      <c r="C172" s="7" t="n"/>
+      <c r="D172" s="7" t="n"/>
+      <c r="G172" s="8" t="n"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="6" t="n"/>
+      <c r="C173" s="7" t="n"/>
+      <c r="D173" s="7" t="n"/>
+      <c r="G173" s="8" t="n"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="6" t="n"/>
+      <c r="C174" s="7" t="n"/>
+      <c r="D174" s="7" t="n"/>
+      <c r="G174" s="8" t="n"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="6" t="n"/>
+      <c r="C175" s="7" t="n"/>
+      <c r="D175" s="7" t="n"/>
+      <c r="G175" s="8" t="n"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="6" t="n"/>
+      <c r="C176" s="7" t="n"/>
+      <c r="D176" s="7" t="n"/>
+      <c r="G176" s="8" t="n"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="6" t="n"/>
+      <c r="C177" s="7" t="n"/>
+      <c r="D177" s="7" t="n"/>
+      <c r="G177" s="8" t="n"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="6" t="n"/>
+      <c r="C178" s="7" t="n"/>
+      <c r="D178" s="7" t="n"/>
+      <c r="G178" s="8" t="n"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="6" t="n"/>
+      <c r="C179" s="7" t="n"/>
+      <c r="D179" s="7" t="n"/>
+      <c r="G179" s="8" t="n"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="6" t="n"/>
+      <c r="C180" s="7" t="n"/>
+      <c r="D180" s="7" t="n"/>
+      <c r="G180" s="8" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="6" t="n"/>
+      <c r="C181" s="7" t="n"/>
+      <c r="D181" s="7" t="n"/>
+      <c r="G181" s="8" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="6" t="n"/>
+      <c r="C182" s="7" t="n"/>
+      <c r="D182" s="7" t="n"/>
+      <c r="G182" s="8" t="n"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="6" t="n"/>
+      <c r="C183" s="7" t="n"/>
+      <c r="D183" s="7" t="n"/>
+      <c r="G183" s="8" t="n"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="6" t="n"/>
+      <c r="C184" s="7" t="n"/>
+      <c r="D184" s="7" t="n"/>
+      <c r="G184" s="8" t="n"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="6" t="n"/>
+      <c r="C185" s="7" t="n"/>
+      <c r="D185" s="7" t="n"/>
+      <c r="G185" s="8" t="n"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="6" t="n"/>
+      <c r="C186" s="7" t="n"/>
+      <c r="D186" s="7" t="n"/>
+      <c r="G186" s="8" t="n"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="6" t="n"/>
+      <c r="C187" s="7" t="n"/>
+      <c r="D187" s="7" t="n"/>
+      <c r="G187" s="8" t="n"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="6" t="n"/>
+      <c r="C188" s="7" t="n"/>
+      <c r="D188" s="7" t="n"/>
+      <c r="G188" s="8" t="n"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="6" t="n"/>
+      <c r="C189" s="7" t="n"/>
+      <c r="D189" s="7" t="n"/>
+      <c r="G189" s="8" t="n"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="6" t="n"/>
+      <c r="C190" s="7" t="n"/>
+      <c r="D190" s="7" t="n"/>
+      <c r="G190" s="8" t="n"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="6" t="n"/>
+      <c r="C191" s="7" t="n"/>
+      <c r="D191" s="7" t="n"/>
+      <c r="G191" s="8" t="n"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="6" t="n"/>
+      <c r="C192" s="7" t="n"/>
+      <c r="D192" s="7" t="n"/>
+      <c r="G192" s="8" t="n"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="6" t="n"/>
+      <c r="C193" s="7" t="n"/>
+      <c r="D193" s="7" t="n"/>
+      <c r="G193" s="8" t="n"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="6" t="n"/>
+      <c r="C194" s="7" t="n"/>
+      <c r="D194" s="7" t="n"/>
+      <c r="G194" s="8" t="n"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="6" t="n"/>
+      <c r="C195" s="7" t="n"/>
+      <c r="D195" s="7" t="n"/>
+      <c r="G195" s="8" t="n"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="6" t="n"/>
+      <c r="C196" s="7" t="n"/>
+      <c r="D196" s="7" t="n"/>
+      <c r="G196" s="8" t="n"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="6" t="n"/>
+      <c r="C197" s="7" t="n"/>
+      <c r="D197" s="7" t="n"/>
+      <c r="G197" s="8" t="n"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="6" t="n"/>
+      <c r="C198" s="7" t="n"/>
+      <c r="D198" s="7" t="n"/>
+      <c r="G198" s="8" t="n"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="6" t="n"/>
+      <c r="C199" s="7" t="n"/>
+      <c r="D199" s="7" t="n"/>
+      <c r="G199" s="8" t="n"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="6" t="n"/>
+      <c r="C200" s="7" t="n"/>
+      <c r="D200" s="7" t="n"/>
+      <c r="G200" s="8" t="n"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="6" t="n"/>
+      <c r="C201" s="7" t="n"/>
+      <c r="D201" s="7" t="n"/>
+      <c r="G201" s="8" t="n"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="6" t="n"/>
+      <c r="C202" s="7" t="n"/>
+      <c r="D202" s="7" t="n"/>
+      <c r="G202" s="8" t="n"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="6" t="n"/>
+      <c r="C203" s="7" t="n"/>
+      <c r="D203" s="7" t="n"/>
+      <c r="G203" s="8" t="n"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="6" t="n"/>
+      <c r="C204" s="7" t="n"/>
+      <c r="D204" s="7" t="n"/>
+      <c r="G204" s="8" t="n"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="6" t="n"/>
+      <c r="C205" s="7" t="n"/>
+      <c r="D205" s="7" t="n"/>
+      <c r="G205" s="8" t="n"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="6" t="n"/>
+      <c r="C206" s="7" t="n"/>
+      <c r="D206" s="7" t="n"/>
+      <c r="G206" s="8" t="n"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="6" t="n"/>
+      <c r="C207" s="7" t="n"/>
+      <c r="D207" s="7" t="n"/>
+      <c r="G207" s="8" t="n"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="6" t="n"/>
+      <c r="C208" s="7" t="n"/>
+      <c r="D208" s="7" t="n"/>
+      <c r="G208" s="8" t="n"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="6" t="n"/>
+      <c r="C209" s="7" t="n"/>
+      <c r="D209" s="7" t="n"/>
+      <c r="G209" s="8" t="n"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="6" t="n"/>
+      <c r="C210" s="7" t="n"/>
+      <c r="D210" s="7" t="n"/>
+      <c r="G210" s="8" t="n"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="6" t="n"/>
+      <c r="C211" s="7" t="n"/>
+      <c r="D211" s="7" t="n"/>
+      <c r="G211" s="8" t="n"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="6" t="n"/>
+      <c r="C212" s="7" t="n"/>
+      <c r="D212" s="7" t="n"/>
+      <c r="G212" s="8" t="n"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="6" t="n"/>
+      <c r="C213" s="7" t="n"/>
+      <c r="D213" s="7" t="n"/>
+      <c r="G213" s="8" t="n"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="6" t="n"/>
+      <c r="C214" s="7" t="n"/>
+      <c r="D214" s="7" t="n"/>
+      <c r="G214" s="8" t="n"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="6" t="n"/>
+      <c r="C215" s="7" t="n"/>
+      <c r="D215" s="7" t="n"/>
+      <c r="G215" s="8" t="n"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="6" t="n"/>
+      <c r="C216" s="7" t="n"/>
+      <c r="D216" s="7" t="n"/>
+      <c r="G216" s="8" t="n"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="6" t="n"/>
+      <c r="C217" s="7" t="n"/>
+      <c r="D217" s="7" t="n"/>
+      <c r="G217" s="8" t="n"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="6" t="n"/>
+      <c r="C218" s="7" t="n"/>
+      <c r="D218" s="7" t="n"/>
+      <c r="G218" s="8" t="n"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="6" t="n"/>
+      <c r="C219" s="7" t="n"/>
+      <c r="D219" s="7" t="n"/>
+      <c r="G219" s="8" t="n"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="6" t="n"/>
+      <c r="C220" s="7" t="n"/>
+      <c r="D220" s="7" t="n"/>
+      <c r="G220" s="8" t="n"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="6" t="n"/>
+      <c r="C221" s="7" t="n"/>
+      <c r="D221" s="7" t="n"/>
+      <c r="G221" s="8" t="n"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="6" t="n"/>
+      <c r="C222" s="7" t="n"/>
+      <c r="D222" s="7" t="n"/>
+      <c r="G222" s="8" t="n"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="6" t="n"/>
+      <c r="C223" s="7" t="n"/>
+      <c r="D223" s="7" t="n"/>
+      <c r="G223" s="8" t="n"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="6" t="n"/>
+      <c r="C224" s="7" t="n"/>
+      <c r="D224" s="7" t="n"/>
+      <c r="G224" s="8" t="n"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="6" t="n"/>
+      <c r="C225" s="7" t="n"/>
+      <c r="D225" s="7" t="n"/>
+      <c r="G225" s="8" t="n"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="6" t="n"/>
+      <c r="C226" s="7" t="n"/>
+      <c r="D226" s="7" t="n"/>
+      <c r="G226" s="8" t="n"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="6" t="n"/>
+      <c r="C227" s="7" t="n"/>
+      <c r="D227" s="7" t="n"/>
+      <c r="G227" s="8" t="n"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="6" t="n"/>
+      <c r="C228" s="7" t="n"/>
+      <c r="D228" s="7" t="n"/>
+      <c r="G228" s="8" t="n"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="6" t="n"/>
+      <c r="C229" s="7" t="n"/>
+      <c r="D229" s="7" t="n"/>
+      <c r="G229" s="8" t="n"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="6" t="n"/>
+      <c r="C230" s="7" t="n"/>
+      <c r="D230" s="7" t="n"/>
+      <c r="G230" s="8" t="n"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="6" t="n"/>
+      <c r="C231" s="7" t="n"/>
+      <c r="D231" s="7" t="n"/>
+      <c r="G231" s="8" t="n"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="6" t="n"/>
+      <c r="C232" s="7" t="n"/>
+      <c r="D232" s="7" t="n"/>
+      <c r="G232" s="8" t="n"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="6" t="n"/>
+      <c r="C233" s="7" t="n"/>
+      <c r="D233" s="7" t="n"/>
+      <c r="G233" s="8" t="n"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="6" t="n"/>
+      <c r="C234" s="7" t="n"/>
+      <c r="D234" s="7" t="n"/>
+      <c r="G234" s="8" t="n"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="6" t="n"/>
+      <c r="C235" s="7" t="n"/>
+      <c r="D235" s="7" t="n"/>
+      <c r="G235" s="8" t="n"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="6" t="n"/>
+      <c r="C236" s="7" t="n"/>
+      <c r="D236" s="7" t="n"/>
+      <c r="G236" s="8" t="n"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="6" t="n"/>
+      <c r="C237" s="7" t="n"/>
+      <c r="D237" s="7" t="n"/>
+      <c r="G237" s="8" t="n"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="6" t="n"/>
+      <c r="C238" s="7" t="n"/>
+      <c r="D238" s="7" t="n"/>
+      <c r="G238" s="8" t="n"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="6" t="n"/>
+      <c r="C239" s="7" t="n"/>
+      <c r="D239" s="7" t="n"/>
+      <c r="G239" s="8" t="n"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="6" t="n"/>
+      <c r="C240" s="7" t="n"/>
+      <c r="D240" s="7" t="n"/>
+      <c r="G240" s="8" t="n"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="6" t="n"/>
+      <c r="C241" s="7" t="n"/>
+      <c r="D241" s="7" t="n"/>
+      <c r="G241" s="8" t="n"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="6" t="n"/>
+      <c r="C242" s="7" t="n"/>
+      <c r="D242" s="7" t="n"/>
+      <c r="G242" s="8" t="n"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="6" t="n"/>
+      <c r="C243" s="7" t="n"/>
+      <c r="D243" s="7" t="n"/>
+      <c r="G243" s="8" t="n"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="6" t="n"/>
+      <c r="C244" s="7" t="n"/>
+      <c r="D244" s="7" t="n"/>
+      <c r="G244" s="8" t="n"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="6" t="n"/>
+      <c r="C245" s="7" t="n"/>
+      <c r="D245" s="7" t="n"/>
+      <c r="G245" s="8" t="n"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="6" t="n"/>
+      <c r="C246" s="7" t="n"/>
+      <c r="D246" s="7" t="n"/>
+      <c r="G246" s="8" t="n"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="6" t="n"/>
+      <c r="C247" s="7" t="n"/>
+      <c r="D247" s="7" t="n"/>
+      <c r="G247" s="8" t="n"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="6" t="n"/>
+      <c r="C248" s="7" t="n"/>
+      <c r="D248" s="7" t="n"/>
+      <c r="G248" s="8" t="n"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="6" t="n"/>
+      <c r="C249" s="7" t="n"/>
+      <c r="D249" s="7" t="n"/>
+      <c r="G249" s="8" t="n"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="6" t="n"/>
+      <c r="C250" s="7" t="n"/>
+      <c r="D250" s="7" t="n"/>
+      <c r="G250" s="8" t="n"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="6" t="n"/>
+      <c r="C251" s="7" t="n"/>
+      <c r="D251" s="7" t="n"/>
+      <c r="G251" s="8" t="n"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="6" t="n"/>
+      <c r="C252" s="7" t="n"/>
+      <c r="D252" s="7" t="n"/>
+      <c r="G252" s="8" t="n"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="6" t="n"/>
+      <c r="C253" s="7" t="n"/>
+      <c r="D253" s="7" t="n"/>
+      <c r="G253" s="8" t="n"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="6" t="n"/>
+      <c r="C254" s="7" t="n"/>
+      <c r="D254" s="7" t="n"/>
+      <c r="G254" s="8" t="n"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="6" t="n"/>
+      <c r="C255" s="7" t="n"/>
+      <c r="D255" s="7" t="n"/>
+      <c r="G255" s="8" t="n"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="6" t="n"/>
+      <c r="C256" s="7" t="n"/>
+      <c r="D256" s="7" t="n"/>
+      <c r="G256" s="8" t="n"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="6" t="n"/>
+      <c r="C257" s="7" t="n"/>
+      <c r="D257" s="7" t="n"/>
+      <c r="G257" s="8" t="n"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="6" t="n"/>
+      <c r="C258" s="7" t="n"/>
+      <c r="D258" s="7" t="n"/>
+      <c r="G258" s="8" t="n"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="6" t="n"/>
+      <c r="C259" s="7" t="n"/>
+      <c r="D259" s="7" t="n"/>
+      <c r="G259" s="8" t="n"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="6" t="n"/>
+      <c r="C260" s="7" t="n"/>
+      <c r="D260" s="7" t="n"/>
+      <c r="G260" s="8" t="n"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="6" t="n"/>
+      <c r="C261" s="7" t="n"/>
+      <c r="D261" s="7" t="n"/>
+      <c r="G261" s="8" t="n"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="6" t="n"/>
+      <c r="C262" s="7" t="n"/>
+      <c r="D262" s="7" t="n"/>
+      <c r="G262" s="8" t="n"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="6" t="n"/>
+      <c r="C263" s="7" t="n"/>
+      <c r="D263" s="7" t="n"/>
+      <c r="G263" s="8" t="n"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="6" t="n"/>
+      <c r="C264" s="7" t="n"/>
+      <c r="D264" s="7" t="n"/>
+      <c r="G264" s="8" t="n"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="6" t="n"/>
+      <c r="C265" s="7" t="n"/>
+      <c r="D265" s="7" t="n"/>
+      <c r="G265" s="8" t="n"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="6" t="n"/>
+      <c r="C266" s="7" t="n"/>
+      <c r="D266" s="7" t="n"/>
+      <c r="G266" s="8" t="n"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="6" t="n"/>
+      <c r="C267" s="7" t="n"/>
+      <c r="D267" s="7" t="n"/>
+      <c r="G267" s="8" t="n"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="6" t="n"/>
+      <c r="C268" s="7" t="n"/>
+      <c r="D268" s="7" t="n"/>
+      <c r="G268" s="8" t="n"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="6" t="n"/>
+      <c r="C269" s="7" t="n"/>
+      <c r="D269" s="7" t="n"/>
+      <c r="G269" s="8" t="n"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="6" t="n"/>
+      <c r="C270" s="7" t="n"/>
+      <c r="D270" s="7" t="n"/>
+      <c r="G270" s="8" t="n"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="6" t="n"/>
+      <c r="C271" s="7" t="n"/>
+      <c r="D271" s="7" t="n"/>
+      <c r="G271" s="8" t="n"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="6" t="n"/>
+      <c r="C272" s="7" t="n"/>
+      <c r="D272" s="7" t="n"/>
+      <c r="G272" s="8" t="n"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="6" t="n"/>
+      <c r="C273" s="7" t="n"/>
+      <c r="D273" s="7" t="n"/>
+      <c r="G273" s="8" t="n"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="6" t="n"/>
+      <c r="C274" s="7" t="n"/>
+      <c r="D274" s="7" t="n"/>
+      <c r="G274" s="8" t="n"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="6" t="n"/>
+      <c r="C275" s="7" t="n"/>
+      <c r="D275" s="7" t="n"/>
+      <c r="G275" s="8" t="n"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="6" t="n"/>
+      <c r="C276" s="7" t="n"/>
+      <c r="D276" s="7" t="n"/>
+      <c r="G276" s="8" t="n"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="6" t="n"/>
+      <c r="C277" s="7" t="n"/>
+      <c r="D277" s="7" t="n"/>
+      <c r="G277" s="8" t="n"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="6" t="n"/>
+      <c r="C278" s="7" t="n"/>
+      <c r="D278" s="7" t="n"/>
+      <c r="G278" s="8" t="n"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="6" t="n"/>
+      <c r="C279" s="7" t="n"/>
+      <c r="D279" s="7" t="n"/>
+      <c r="G279" s="8" t="n"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="6" t="n"/>
+      <c r="C280" s="7" t="n"/>
+      <c r="D280" s="7" t="n"/>
+      <c r="G280" s="8" t="n"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="6" t="n"/>
+      <c r="C281" s="7" t="n"/>
+      <c r="D281" s="7" t="n"/>
+      <c r="G281" s="8" t="n"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="6" t="n"/>
+      <c r="C282" s="7" t="n"/>
+      <c r="D282" s="7" t="n"/>
+      <c r="G282" s="8" t="n"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="6" t="n"/>
+      <c r="C283" s="7" t="n"/>
+      <c r="D283" s="7" t="n"/>
+      <c r="G283" s="8" t="n"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="6" t="n"/>
+      <c r="C284" s="7" t="n"/>
+      <c r="D284" s="7" t="n"/>
+      <c r="G284" s="8" t="n"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="6" t="n"/>
+      <c r="C285" s="7" t="n"/>
+      <c r="D285" s="7" t="n"/>
+      <c r="G285" s="8" t="n"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="6" t="n"/>
+      <c r="C286" s="7" t="n"/>
+      <c r="D286" s="7" t="n"/>
+      <c r="G286" s="8" t="n"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="6" t="n"/>
+      <c r="C287" s="7" t="n"/>
+      <c r="D287" s="7" t="n"/>
+      <c r="G287" s="8" t="n"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="6" t="n"/>
+      <c r="C288" s="7" t="n"/>
+      <c r="D288" s="7" t="n"/>
+      <c r="G288" s="8" t="n"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="6" t="n"/>
+      <c r="C289" s="7" t="n"/>
+      <c r="D289" s="7" t="n"/>
+      <c r="G289" s="8" t="n"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="6" t="n"/>
+      <c r="C290" s="7" t="n"/>
+      <c r="D290" s="7" t="n"/>
+      <c r="G290" s="8" t="n"/>
+    </row>
+    <row r="291">
+      <c r="A291" s="6" t="n"/>
+      <c r="C291" s="7" t="n"/>
+      <c r="D291" s="7" t="n"/>
+      <c r="G291" s="8" t="n"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="6" t="n"/>
+      <c r="C292" s="7" t="n"/>
+      <c r="D292" s="7" t="n"/>
+      <c r="G292" s="8" t="n"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="6" t="n"/>
+      <c r="C293" s="7" t="n"/>
+      <c r="D293" s="7" t="n"/>
+      <c r="G293" s="8" t="n"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="6" t="n"/>
+      <c r="C294" s="7" t="n"/>
+      <c r="D294" s="7" t="n"/>
+      <c r="G294" s="8" t="n"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="6" t="n"/>
+      <c r="C295" s="7" t="n"/>
+      <c r="D295" s="7" t="n"/>
+      <c r="G295" s="8" t="n"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="6" t="n"/>
+      <c r="C296" s="7" t="n"/>
+      <c r="D296" s="7" t="n"/>
+      <c r="G296" s="8" t="n"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="6" t="n"/>
+      <c r="C297" s="7" t="n"/>
+      <c r="D297" s="7" t="n"/>
+      <c r="G297" s="8" t="n"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="6" t="n"/>
+      <c r="C298" s="7" t="n"/>
+      <c r="D298" s="7" t="n"/>
+      <c r="G298" s="8" t="n"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="6" t="n"/>
+      <c r="C299" s="7" t="n"/>
+      <c r="D299" s="7" t="n"/>
+      <c r="G299" s="8" t="n"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="6" t="n"/>
+      <c r="C300" s="7" t="n"/>
+      <c r="D300" s="7" t="n"/>
+      <c r="G300" s="8" t="n"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="6" t="n"/>
+      <c r="C301" s="7" t="n"/>
+      <c r="D301" s="7" t="n"/>
+      <c r="G301" s="8" t="n"/>
+    </row>
+    <row r="302">
+      <c r="A302" s="6" t="n"/>
+      <c r="C302" s="7" t="n"/>
+      <c r="D302" s="7" t="n"/>
+      <c r="G302" s="8" t="n"/>
+    </row>
+    <row r="303">
+      <c r="A303" s="6" t="n"/>
+      <c r="C303" s="7" t="n"/>
+      <c r="D303" s="7" t="n"/>
+      <c r="G303" s="8" t="n"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="6" t="n"/>
+      <c r="C304" s="7" t="n"/>
+      <c r="D304" s="7" t="n"/>
+      <c r="G304" s="8" t="n"/>
+    </row>
+    <row r="305">
+      <c r="A305" s="6" t="n"/>
+      <c r="C305" s="7" t="n"/>
+      <c r="D305" s="7" t="n"/>
+      <c r="G305" s="8" t="n"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="6" t="n"/>
+      <c r="C306" s="7" t="n"/>
+      <c r="D306" s="7" t="n"/>
+      <c r="G306" s="8" t="n"/>
+    </row>
+    <row r="307">
+      <c r="A307" s="6" t="n"/>
+      <c r="C307" s="7" t="n"/>
+      <c r="D307" s="7" t="n"/>
+      <c r="G307" s="8" t="n"/>
+    </row>
+    <row r="308">
+      <c r="A308" s="6" t="n"/>
+      <c r="C308" s="7" t="n"/>
+      <c r="D308" s="7" t="n"/>
+      <c r="G308" s="8" t="n"/>
+    </row>
+    <row r="309">
+      <c r="A309" s="6" t="n"/>
+      <c r="C309" s="7" t="n"/>
+      <c r="D309" s="7" t="n"/>
+      <c r="G309" s="8" t="n"/>
+    </row>
+    <row r="310">
+      <c r="A310" s="6" t="n"/>
+      <c r="C310" s="7" t="n"/>
+      <c r="D310" s="7" t="n"/>
+      <c r="G310" s="8" t="n"/>
+    </row>
+    <row r="311">
+      <c r="A311" s="6" t="n"/>
+      <c r="C311" s="7" t="n"/>
+      <c r="D311" s="7" t="n"/>
+      <c r="G311" s="8" t="n"/>
+    </row>
+    <row r="312">
+      <c r="A312" s="6" t="n"/>
+      <c r="C312" s="7" t="n"/>
+      <c r="D312" s="7" t="n"/>
+      <c r="G312" s="8" t="n"/>
+    </row>
+    <row r="313">
+      <c r="A313" s="6" t="n"/>
+      <c r="C313" s="7" t="n"/>
+      <c r="D313" s="7" t="n"/>
+      <c r="G313" s="8" t="n"/>
+    </row>
+    <row r="314">
+      <c r="A314" s="6" t="n"/>
+      <c r="C314" s="7" t="n"/>
+      <c r="D314" s="7" t="n"/>
+      <c r="G314" s="8" t="n"/>
+    </row>
+    <row r="315">
+      <c r="A315" s="6" t="n"/>
+      <c r="C315" s="7" t="n"/>
+      <c r="D315" s="7" t="n"/>
+      <c r="G315" s="8" t="n"/>
+    </row>
+    <row r="316">
+      <c r="A316" s="6" t="n"/>
+      <c r="C316" s="7" t="n"/>
+      <c r="D316" s="7" t="n"/>
+      <c r="G316" s="8" t="n"/>
+    </row>
+    <row r="317">
+      <c r="A317" s="6" t="n"/>
+      <c r="C317" s="7" t="n"/>
+      <c r="D317" s="7" t="n"/>
+      <c r="G317" s="8" t="n"/>
+    </row>
+    <row r="318">
+      <c r="A318" s="6" t="n"/>
+      <c r="C318" s="7" t="n"/>
+      <c r="D318" s="7" t="n"/>
+      <c r="G318" s="8" t="n"/>
+    </row>
+    <row r="319">
+      <c r="A319" s="6" t="n"/>
+      <c r="C319" s="7" t="n"/>
+      <c r="D319" s="7" t="n"/>
+      <c r="G319" s="8" t="n"/>
+    </row>
+    <row r="320">
+      <c r="A320" s="6" t="n"/>
+      <c r="C320" s="7" t="n"/>
+      <c r="D320" s="7" t="n"/>
+      <c r="G320" s="8" t="n"/>
+    </row>
+    <row r="321">
+      <c r="A321" s="6" t="n"/>
+      <c r="C321" s="7" t="n"/>
+      <c r="D321" s="7" t="n"/>
+      <c r="G321" s="8" t="n"/>
+    </row>
+    <row r="322">
+      <c r="A322" s="6" t="n"/>
+      <c r="C322" s="7" t="n"/>
+      <c r="D322" s="7" t="n"/>
+      <c r="G322" s="8" t="n"/>
+    </row>
+    <row r="323">
+      <c r="A323" s="6" t="n"/>
+      <c r="C323" s="7" t="n"/>
+      <c r="D323" s="7" t="n"/>
+      <c r="G323" s="8" t="n"/>
+    </row>
+    <row r="324">
+      <c r="A324" s="6" t="n"/>
+      <c r="C324" s="7" t="n"/>
+      <c r="D324" s="7" t="n"/>
+      <c r="G324" s="8" t="n"/>
+    </row>
+    <row r="325">
+      <c r="A325" s="6" t="n"/>
+      <c r="C325" s="7" t="n"/>
+      <c r="D325" s="7" t="n"/>
+      <c r="G325" s="8" t="n"/>
+    </row>
+    <row r="326">
+      <c r="A326" s="6" t="n"/>
+      <c r="C326" s="7" t="n"/>
+      <c r="D326" s="7" t="n"/>
+      <c r="G326" s="8" t="n"/>
+    </row>
+    <row r="327">
+      <c r="A327" s="6" t="n"/>
+      <c r="C327" s="7" t="n"/>
+      <c r="D327" s="7" t="n"/>
+      <c r="G327" s="8" t="n"/>
+    </row>
+    <row r="328">
+      <c r="A328" s="6" t="n"/>
+      <c r="C328" s="7" t="n"/>
+      <c r="D328" s="7" t="n"/>
+      <c r="G328" s="8" t="n"/>
+    </row>
+    <row r="329">
+      <c r="A329" s="6" t="n"/>
+      <c r="C329" s="7" t="n"/>
+      <c r="D329" s="7" t="n"/>
+      <c r="G329" s="8" t="n"/>
+    </row>
+    <row r="330">
+      <c r="A330" s="6" t="n"/>
+      <c r="C330" s="7" t="n"/>
+      <c r="D330" s="7" t="n"/>
+      <c r="G330" s="8" t="n"/>
+    </row>
+    <row r="331">
+      <c r="A331" s="6" t="n"/>
+      <c r="C331" s="7" t="n"/>
+      <c r="D331" s="7" t="n"/>
+      <c r="G331" s="8" t="n"/>
+    </row>
+    <row r="332">
+      <c r="A332" s="6" t="n"/>
+      <c r="C332" s="7" t="n"/>
+      <c r="D332" s="7" t="n"/>
+      <c r="G332" s="8" t="n"/>
+    </row>
+    <row r="333">
+      <c r="A333" s="6" t="n"/>
+      <c r="C333" s="7" t="n"/>
+      <c r="D333" s="7" t="n"/>
+      <c r="G333" s="8" t="n"/>
+    </row>
+    <row r="334">
+      <c r="A334" s="6" t="n"/>
+      <c r="C334" s="7" t="n"/>
+      <c r="D334" s="7" t="n"/>
+      <c r="G334" s="8" t="n"/>
+    </row>
+    <row r="335">
+      <c r="A335" s="6" t="n"/>
+      <c r="C335" s="7" t="n"/>
+      <c r="D335" s="7" t="n"/>
+      <c r="G335" s="8" t="n"/>
+    </row>
+    <row r="336">
+      <c r="A336" s="6" t="n"/>
+      <c r="C336" s="7" t="n"/>
+      <c r="D336" s="7" t="n"/>
+      <c r="G336" s="8" t="n"/>
+    </row>
+    <row r="337">
+      <c r="A337" s="6" t="n"/>
+      <c r="C337" s="7" t="n"/>
+      <c r="D337" s="7" t="n"/>
+      <c r="G337" s="8" t="n"/>
+    </row>
+    <row r="338">
+      <c r="A338" s="6" t="n"/>
+      <c r="C338" s="7" t="n"/>
+      <c r="D338" s="7" t="n"/>
+      <c r="G338" s="8" t="n"/>
+    </row>
+    <row r="339">
+      <c r="A339" s="6" t="n"/>
+      <c r="C339" s="7" t="n"/>
+      <c r="D339" s="7" t="n"/>
+      <c r="G339" s="8" t="n"/>
+    </row>
+    <row r="340">
+      <c r="A340" s="6" t="n"/>
+      <c r="C340" s="7" t="n"/>
+      <c r="D340" s="7" t="n"/>
+      <c r="G340" s="8" t="n"/>
+    </row>
+    <row r="341">
+      <c r="A341" s="6" t="n"/>
+      <c r="C341" s="7" t="n"/>
+      <c r="D341" s="7" t="n"/>
+      <c r="G341" s="8" t="n"/>
+    </row>
+    <row r="342">
+      <c r="A342" s="6" t="n"/>
+      <c r="C342" s="7" t="n"/>
+      <c r="D342" s="7" t="n"/>
+      <c r="G342" s="8" t="n"/>
+    </row>
+    <row r="343">
+      <c r="A343" s="6" t="n"/>
+      <c r="C343" s="7" t="n"/>
+      <c r="D343" s="7" t="n"/>
+      <c r="G343" s="8" t="n"/>
+    </row>
+    <row r="344">
+      <c r="A344" s="6" t="n"/>
+      <c r="C344" s="7" t="n"/>
+      <c r="D344" s="7" t="n"/>
+      <c r="G344" s="8" t="n"/>
+    </row>
+    <row r="345">
+      <c r="A345" s="6" t="n"/>
+      <c r="C345" s="7" t="n"/>
+      <c r="D345" s="7" t="n"/>
+      <c r="G345" s="8" t="n"/>
+    </row>
+    <row r="346">
+      <c r="A346" s="6" t="n"/>
+      <c r="C346" s="7" t="n"/>
+      <c r="D346" s="7" t="n"/>
+      <c r="G346" s="8" t="n"/>
+    </row>
+    <row r="347">
+      <c r="A347" s="6" t="n"/>
+      <c r="C347" s="7" t="n"/>
+      <c r="D347" s="7" t="n"/>
+      <c r="G347" s="8" t="n"/>
+    </row>
+    <row r="348">
+      <c r="A348" s="6" t="n"/>
+      <c r="C348" s="7" t="n"/>
+      <c r="D348" s="7" t="n"/>
+      <c r="G348" s="8" t="n"/>
+    </row>
+    <row r="349">
+      <c r="A349" s="6" t="n"/>
+      <c r="C349" s="7" t="n"/>
+      <c r="D349" s="7" t="n"/>
+      <c r="G349" s="8" t="n"/>
+    </row>
+    <row r="350">
+      <c r="A350" s="6" t="n"/>
+      <c r="C350" s="7" t="n"/>
+      <c r="D350" s="7" t="n"/>
+      <c r="G350" s="8" t="n"/>
+    </row>
+    <row r="351">
+      <c r="A351" s="6" t="n"/>
+      <c r="C351" s="7" t="n"/>
+      <c r="D351" s="7" t="n"/>
+      <c r="G351" s="8" t="n"/>
+    </row>
+    <row r="352">
+      <c r="A352" s="6" t="n"/>
+      <c r="C352" s="7" t="n"/>
+      <c r="D352" s="7" t="n"/>
+      <c r="G352" s="8" t="n"/>
+    </row>
+    <row r="353">
+      <c r="A353" s="6" t="n"/>
+      <c r="C353" s="7" t="n"/>
+      <c r="D353" s="7" t="n"/>
+      <c r="G353" s="8" t="n"/>
+    </row>
+    <row r="354">
+      <c r="A354" s="6" t="n"/>
+      <c r="C354" s="7" t="n"/>
+      <c r="D354" s="7" t="n"/>
+      <c r="G354" s="8" t="n"/>
+    </row>
+    <row r="355">
+      <c r="A355" s="6" t="n"/>
+      <c r="C355" s="7" t="n"/>
+      <c r="D355" s="7" t="n"/>
+      <c r="G355" s="8" t="n"/>
+    </row>
+    <row r="356">
+      <c r="A356" s="6" t="n"/>
+      <c r="C356" s="7" t="n"/>
+      <c r="D356" s="7" t="n"/>
+      <c r="G356" s="8" t="n"/>
+    </row>
+    <row r="357">
+      <c r="A357" s="6" t="n"/>
+      <c r="C357" s="7" t="n"/>
+      <c r="D357" s="7" t="n"/>
+      <c r="G357" s="8" t="n"/>
+    </row>
+    <row r="358">
+      <c r="A358" s="6" t="n"/>
+      <c r="C358" s="7" t="n"/>
+      <c r="D358" s="7" t="n"/>
+      <c r="G358" s="8" t="n"/>
+    </row>
+    <row r="359">
+      <c r="A359" s="6" t="n"/>
+      <c r="C359" s="7" t="n"/>
+      <c r="D359" s="7" t="n"/>
+      <c r="G359" s="8" t="n"/>
+    </row>
+    <row r="360">
+      <c r="A360" s="6" t="n"/>
+      <c r="C360" s="7" t="n"/>
+      <c r="D360" s="7" t="n"/>
+      <c r="G360" s="8" t="n"/>
+    </row>
+    <row r="361">
+      <c r="A361" s="6" t="n"/>
+      <c r="C361" s="7" t="n"/>
+      <c r="D361" s="7" t="n"/>
+      <c r="G361" s="8" t="n"/>
+    </row>
+    <row r="362">
+      <c r="A362" s="6" t="n"/>
+      <c r="C362" s="7" t="n"/>
+      <c r="D362" s="7" t="n"/>
+      <c r="G362" s="8" t="n"/>
+    </row>
+    <row r="363">
+      <c r="A363" s="6" t="n"/>
+      <c r="C363" s="7" t="n"/>
+      <c r="D363" s="7" t="n"/>
+      <c r="G363" s="8" t="n"/>
+    </row>
+    <row r="364">
+      <c r="A364" s="6" t="n"/>
+      <c r="C364" s="7" t="n"/>
+      <c r="D364" s="7" t="n"/>
+      <c r="G364" s="8" t="n"/>
+    </row>
+    <row r="365">
+      <c r="A365" s="6" t="n"/>
+      <c r="C365" s="7" t="n"/>
+      <c r="D365" s="7" t="n"/>
+      <c r="G365" s="8" t="n"/>
+    </row>
+    <row r="366">
+      <c r="A366" s="6" t="n"/>
+      <c r="C366" s="7" t="n"/>
+      <c r="D366" s="7" t="n"/>
+      <c r="G366" s="8" t="n"/>
+    </row>
+    <row r="367">
+      <c r="A367" s="6" t="n"/>
+      <c r="C367" s="7" t="n"/>
+      <c r="D367" s="7" t="n"/>
+      <c r="G367" s="8" t="n"/>
+    </row>
+    <row r="368">
+      <c r="A368" s="6" t="n"/>
+      <c r="C368" s="7" t="n"/>
+      <c r="D368" s="7" t="n"/>
+      <c r="G368" s="8" t="n"/>
+    </row>
+    <row r="369">
+      <c r="A369" s="6" t="n"/>
+      <c r="C369" s="7" t="n"/>
+      <c r="D369" s="7" t="n"/>
+      <c r="G369" s="8" t="n"/>
+    </row>
+    <row r="370">
+      <c r="A370" s="6" t="n"/>
+      <c r="C370" s="7" t="n"/>
+      <c r="D370" s="7" t="n"/>
+      <c r="G370" s="8" t="n"/>
+    </row>
+    <row r="371">
+      <c r="A371" s="6" t="n"/>
+      <c r="C371" s="7" t="n"/>
+      <c r="D371" s="7" t="n"/>
+      <c r="G371" s="8" t="n"/>
+    </row>
+    <row r="372">
+      <c r="A372" s="6" t="n"/>
+      <c r="C372" s="7" t="n"/>
+      <c r="D372" s="7" t="n"/>
+      <c r="G372" s="8" t="n"/>
+    </row>
+    <row r="373">
+      <c r="A373" s="6" t="n"/>
+      <c r="C373" s="7" t="n"/>
+      <c r="D373" s="7" t="n"/>
+      <c r="G373" s="8" t="n"/>
+    </row>
+    <row r="374">
+      <c r="A374" s="6" t="n"/>
+      <c r="C374" s="7" t="n"/>
+      <c r="D374" s="7" t="n"/>
+      <c r="G374" s="8" t="n"/>
+    </row>
+    <row r="375">
+      <c r="A375" s="6" t="n"/>
+      <c r="C375" s="7" t="n"/>
+      <c r="D375" s="7" t="n"/>
+      <c r="G375" s="8" t="n"/>
+    </row>
+    <row r="376">
+      <c r="A376" s="6" t="n"/>
+      <c r="C376" s="7" t="n"/>
+      <c r="D376" s="7" t="n"/>
+      <c r="G376" s="8" t="n"/>
+    </row>
+    <row r="377">
+      <c r="A377" s="6" t="n"/>
+      <c r="C377" s="7" t="n"/>
+      <c r="D377" s="7" t="n"/>
+      <c r="G377" s="8" t="n"/>
+    </row>
+    <row r="378">
+      <c r="A378" s="6" t="n"/>
+      <c r="C378" s="7" t="n"/>
+      <c r="D378" s="7" t="n"/>
+      <c r="G378" s="8" t="n"/>
+    </row>
+    <row r="379">
+      <c r="A379" s="6" t="n"/>
+      <c r="C379" s="7" t="n"/>
+      <c r="D379" s="7" t="n"/>
+      <c r="G379" s="8" t="n"/>
+    </row>
+    <row r="380">
+      <c r="A380" s="6" t="n"/>
+      <c r="C380" s="7" t="n"/>
+      <c r="D380" s="7" t="n"/>
+      <c r="G380" s="8" t="n"/>
+    </row>
+    <row r="381">
+      <c r="A381" s="6" t="n"/>
+      <c r="C381" s="7" t="n"/>
+      <c r="D381" s="7" t="n"/>
+      <c r="G381" s="8" t="n"/>
+    </row>
+    <row r="382">
+      <c r="A382" s="6" t="n"/>
+      <c r="C382" s="7" t="n"/>
+      <c r="D382" s="7" t="n"/>
+      <c r="G382" s="8" t="n"/>
+    </row>
+    <row r="383">
+      <c r="A383" s="6" t="n"/>
+      <c r="C383" s="7" t="n"/>
+      <c r="D383" s="7" t="n"/>
+      <c r="G383" s="8" t="n"/>
+    </row>
+    <row r="384">
+      <c r="A384" s="6" t="n"/>
+      <c r="C384" s="7" t="n"/>
+      <c r="D384" s="7" t="n"/>
+      <c r="G384" s="8" t="n"/>
+    </row>
+    <row r="385">
+      <c r="A385" s="6" t="n"/>
+      <c r="C385" s="7" t="n"/>
+      <c r="D385" s="7" t="n"/>
+      <c r="G385" s="8" t="n"/>
+    </row>
+    <row r="386">
+      <c r="A386" s="6" t="n"/>
+      <c r="C386" s="7" t="n"/>
+      <c r="D386" s="7" t="n"/>
+      <c r="G386" s="8" t="n"/>
+    </row>
+    <row r="387">
+      <c r="A387" s="6" t="n"/>
+      <c r="C387" s="7" t="n"/>
+      <c r="D387" s="7" t="n"/>
+      <c r="G387" s="8" t="n"/>
+    </row>
+    <row r="388">
+      <c r="A388" s="6" t="n"/>
+      <c r="C388" s="7" t="n"/>
+      <c r="D388" s="7" t="n"/>
+      <c r="G388" s="8" t="n"/>
+    </row>
+    <row r="389">
+      <c r="A389" s="6" t="n"/>
+      <c r="C389" s="7" t="n"/>
+      <c r="D389" s="7" t="n"/>
+      <c r="G389" s="8" t="n"/>
+    </row>
+    <row r="390">
+      <c r="A390" s="6" t="n"/>
+      <c r="C390" s="7" t="n"/>
+      <c r="D390" s="7" t="n"/>
+      <c r="G390" s="8" t="n"/>
+    </row>
+    <row r="391">
+      <c r="A391" s="6" t="n"/>
+      <c r="C391" s="7" t="n"/>
+      <c r="D391" s="7" t="n"/>
+      <c r="G391" s="8" t="n"/>
+    </row>
+    <row r="392">
+      <c r="A392" s="6" t="n"/>
+      <c r="C392" s="7" t="n"/>
+      <c r="D392" s="7" t="n"/>
+      <c r="G392" s="8" t="n"/>
+    </row>
+    <row r="393">
+      <c r="A393" s="6" t="n"/>
+      <c r="C393" s="7" t="n"/>
+      <c r="D393" s="7" t="n"/>
+      <c r="G393" s="8" t="n"/>
+    </row>
+    <row r="394">
+      <c r="A394" s="6" t="n"/>
+      <c r="C394" s="7" t="n"/>
+      <c r="D394" s="7" t="n"/>
+      <c r="G394" s="8" t="n"/>
+    </row>
+    <row r="395">
+      <c r="A395" s="6" t="n"/>
+      <c r="C395" s="7" t="n"/>
+      <c r="D395" s="7" t="n"/>
+      <c r="G395" s="8" t="n"/>
+    </row>
+    <row r="396">
+      <c r="A396" s="6" t="n"/>
+      <c r="C396" s="7" t="n"/>
+      <c r="D396" s="7" t="n"/>
+      <c r="G396" s="8" t="n"/>
+    </row>
+    <row r="397">
+      <c r="A397" s="6" t="n"/>
+      <c r="C397" s="7" t="n"/>
+      <c r="D397" s="7" t="n"/>
+      <c r="G397" s="8" t="n"/>
+    </row>
+    <row r="398">
+      <c r="A398" s="6" t="n"/>
+      <c r="C398" s="7" t="n"/>
+      <c r="D398" s="7" t="n"/>
+      <c r="G398" s="8" t="n"/>
+    </row>
+    <row r="399">
+      <c r="A399" s="6" t="n"/>
+      <c r="C399" s="7" t="n"/>
+      <c r="D399" s="7" t="n"/>
+      <c r="G399" s="8" t="n"/>
+    </row>
+    <row r="400">
+      <c r="A400" s="6" t="n"/>
+      <c r="C400" s="7" t="n"/>
+      <c r="D400" s="7" t="n"/>
+      <c r="G400" s="8" t="n"/>
+    </row>
+    <row r="401">
+      <c r="A401" s="6" t="n"/>
+      <c r="C401" s="7" t="n"/>
+      <c r="D401" s="7" t="n"/>
+      <c r="G401" s="8" t="n"/>
+    </row>
+    <row r="402">
+      <c r="A402" s="6" t="n"/>
+      <c r="C402" s="7" t="n"/>
+      <c r="D402" s="7" t="n"/>
+      <c r="G402" s="8" t="n"/>
+    </row>
+    <row r="403">
+      <c r="A403" s="6" t="n"/>
+      <c r="C403" s="7" t="n"/>
+      <c r="D403" s="7" t="n"/>
+      <c r="G403" s="8" t="n"/>
+    </row>
+    <row r="404">
+      <c r="A404" s="6" t="n"/>
+      <c r="C404" s="7" t="n"/>
+      <c r="D404" s="7" t="n"/>
+      <c r="G404" s="8" t="n"/>
+    </row>
+    <row r="405">
+      <c r="A405" s="6" t="n"/>
+      <c r="C405" s="7" t="n"/>
+      <c r="D405" s="7" t="n"/>
+      <c r="G405" s="8" t="n"/>
+    </row>
+    <row r="406">
+      <c r="A406" s="6" t="n"/>
+      <c r="C406" s="7" t="n"/>
+      <c r="D406" s="7" t="n"/>
+      <c r="G406" s="8" t="n"/>
+    </row>
+    <row r="407">
+      <c r="A407" s="6" t="n"/>
+      <c r="C407" s="7" t="n"/>
+      <c r="D407" s="7" t="n"/>
+      <c r="G407" s="8" t="n"/>
+    </row>
+    <row r="408">
+      <c r="A408" s="6" t="n"/>
+      <c r="C408" s="7" t="n"/>
+      <c r="D408" s="7" t="n"/>
+      <c r="G408" s="8" t="n"/>
+    </row>
+    <row r="409">
+      <c r="A409" s="6" t="n"/>
+      <c r="C409" s="7" t="n"/>
+      <c r="D409" s="7" t="n"/>
+      <c r="G409" s="8" t="n"/>
+    </row>
+    <row r="410">
+      <c r="A410" s="6" t="n"/>
+      <c r="C410" s="7" t="n"/>
+      <c r="D410" s="7" t="n"/>
+      <c r="G410" s="8" t="n"/>
+    </row>
+    <row r="411">
+      <c r="A411" s="6" t="n"/>
+      <c r="C411" s="7" t="n"/>
+      <c r="D411" s="7" t="n"/>
+      <c r="G411" s="8" t="n"/>
+    </row>
+    <row r="412">
+      <c r="A412" s="6" t="n"/>
+      <c r="C412" s="7" t="n"/>
+      <c r="D412" s="7" t="n"/>
+      <c r="G412" s="8" t="n"/>
+    </row>
+    <row r="413">
+      <c r="A413" s="6" t="n"/>
+      <c r="C413" s="7" t="n"/>
+      <c r="D413" s="7" t="n"/>
+      <c r="G413" s="8" t="n"/>
+    </row>
+    <row r="414">
+      <c r="A414" s="6" t="n"/>
+      <c r="C414" s="7" t="n"/>
+      <c r="D414" s="7" t="n"/>
+      <c r="G414" s="8" t="n"/>
+    </row>
+    <row r="415">
+      <c r="A415" s="6" t="n"/>
+      <c r="C415" s="7" t="n"/>
+      <c r="D415" s="7" t="n"/>
+      <c r="G415" s="8" t="n"/>
+    </row>
+    <row r="416">
+      <c r="A416" s="6" t="n"/>
+      <c r="C416" s="7" t="n"/>
+      <c r="D416" s="7" t="n"/>
+      <c r="G416" s="8" t="n"/>
+    </row>
+    <row r="417">
+      <c r="A417" s="6" t="n"/>
+      <c r="C417" s="7" t="n"/>
+      <c r="D417" s="7" t="n"/>
+      <c r="G417" s="8" t="n"/>
+    </row>
+    <row r="418">
+      <c r="A418" s="6" t="n"/>
+      <c r="C418" s="7" t="n"/>
+      <c r="D418" s="7" t="n"/>
+      <c r="G418" s="8" t="n"/>
+    </row>
+    <row r="419">
+      <c r="A419" s="6" t="n"/>
+      <c r="C419" s="7" t="n"/>
+      <c r="D419" s="7" t="n"/>
+      <c r="G419" s="8" t="n"/>
+    </row>
+    <row r="420">
+      <c r="A420" s="6" t="n"/>
+      <c r="C420" s="7" t="n"/>
+      <c r="D420" s="7" t="n"/>
+      <c r="G420" s="8" t="n"/>
+    </row>
+    <row r="421">
+      <c r="A421" s="6" t="n"/>
+      <c r="C421" s="7" t="n"/>
+      <c r="D421" s="7" t="n"/>
+      <c r="G421" s="8" t="n"/>
+    </row>
+    <row r="422">
+      <c r="A422" s="6" t="n"/>
+      <c r="C422" s="7" t="n"/>
+      <c r="D422" s="7" t="n"/>
+      <c r="G422" s="8" t="n"/>
+    </row>
+    <row r="423">
+      <c r="A423" s="6" t="n"/>
+      <c r="C423" s="7" t="n"/>
+      <c r="D423" s="7" t="n"/>
+      <c r="G423" s="8" t="n"/>
+    </row>
+    <row r="424">
+      <c r="A424" s="6" t="n"/>
+      <c r="C424" s="7" t="n"/>
+      <c r="D424" s="7" t="n"/>
+      <c r="G424" s="8" t="n"/>
+    </row>
+    <row r="425">
+      <c r="A425" s="6" t="n"/>
+      <c r="C425" s="7" t="n"/>
+      <c r="D425" s="7" t="n"/>
+      <c r="G425" s="8" t="n"/>
+    </row>
+    <row r="426">
+      <c r="A426" s="6" t="n"/>
+      <c r="C426" s="7" t="n"/>
+      <c r="D426" s="7" t="n"/>
+      <c r="G426" s="8" t="n"/>
+    </row>
+    <row r="427">
+      <c r="A427" s="6" t="n"/>
+      <c r="C427" s="7" t="n"/>
+      <c r="D427" s="7" t="n"/>
+      <c r="G427" s="8" t="n"/>
+    </row>
+    <row r="428">
+      <c r="A428" s="6" t="n"/>
+      <c r="C428" s="7" t="n"/>
+      <c r="D428" s="7" t="n"/>
+      <c r="G428" s="8" t="n"/>
+    </row>
+    <row r="429">
+      <c r="A429" s="6" t="n"/>
+      <c r="C429" s="7" t="n"/>
+      <c r="D429" s="7" t="n"/>
+      <c r="G429" s="8" t="n"/>
+    </row>
+    <row r="430">
+      <c r="A430" s="6" t="n"/>
+      <c r="C430" s="7" t="n"/>
+      <c r="D430" s="7" t="n"/>
+      <c r="G430" s="8" t="n"/>
+    </row>
+    <row r="431">
+      <c r="A431" s="6" t="n"/>
+      <c r="C431" s="7" t="n"/>
+      <c r="D431" s="7" t="n"/>
+      <c r="G431" s="8" t="n"/>
+    </row>
+    <row r="432">
+      <c r="A432" s="6" t="n"/>
+      <c r="C432" s="7" t="n"/>
+      <c r="D432" s="7" t="n"/>
+      <c r="G432" s="8" t="n"/>
+    </row>
+    <row r="433">
+      <c r="A433" s="6" t="n"/>
+      <c r="C433" s="7" t="n"/>
+      <c r="D433" s="7" t="n"/>
+      <c r="G433" s="8" t="n"/>
+    </row>
+    <row r="434">
+      <c r="A434" s="6" t="n"/>
+      <c r="C434" s="7" t="n"/>
+      <c r="D434" s="7" t="n"/>
+      <c r="G434" s="8" t="n"/>
+    </row>
+    <row r="435">
+      <c r="A435" s="6" t="n"/>
+      <c r="C435" s="7" t="n"/>
+      <c r="D435" s="7" t="n"/>
+      <c r="G435" s="8" t="n"/>
+    </row>
+    <row r="436">
+      <c r="A436" s="6" t="n"/>
+      <c r="C436" s="7" t="n"/>
+      <c r="D436" s="7" t="n"/>
+      <c r="G436" s="8" t="n"/>
+    </row>
+    <row r="437">
+      <c r="A437" s="6" t="n"/>
+      <c r="C437" s="7" t="n"/>
+      <c r="D437" s="7" t="n"/>
+      <c r="G437" s="8" t="n"/>
+    </row>
+    <row r="438">
+      <c r="A438" s="6" t="n"/>
+      <c r="C438" s="7" t="n"/>
+      <c r="D438" s="7" t="n"/>
+      <c r="G438" s="8" t="n"/>
+    </row>
+    <row r="439">
+      <c r="A439" s="6" t="n"/>
+      <c r="C439" s="7" t="n"/>
+      <c r="D439" s="7" t="n"/>
+      <c r="G439" s="8" t="n"/>
+    </row>
+    <row r="440">
+      <c r="A440" s="6" t="n"/>
+      <c r="C440" s="7" t="n"/>
+      <c r="D440" s="7" t="n"/>
+      <c r="G440" s="8" t="n"/>
+    </row>
+    <row r="441">
+      <c r="A441" s="6" t="n"/>
+      <c r="C441" s="7" t="n"/>
+      <c r="D441" s="7" t="n"/>
+      <c r="G441" s="8" t="n"/>
+    </row>
+    <row r="442">
+      <c r="A442" s="6" t="n"/>
+      <c r="C442" s="7" t="n"/>
+      <c r="D442" s="7" t="n"/>
+      <c r="G442" s="8" t="n"/>
+    </row>
+    <row r="443">
+      <c r="A443" s="6" t="n"/>
+      <c r="C443" s="7" t="n"/>
+      <c r="D443" s="7" t="n"/>
+      <c r="G443" s="8" t="n"/>
+    </row>
+    <row r="444">
+      <c r="A444" s="6" t="n"/>
+      <c r="C444" s="7" t="n"/>
+      <c r="D444" s="7" t="n"/>
+      <c r="G444" s="8" t="n"/>
+    </row>
+    <row r="445">
+      <c r="A445" s="6" t="n"/>
+      <c r="C445" s="7" t="n"/>
+      <c r="D445" s="7" t="n"/>
+      <c r="G445" s="8" t="n"/>
+    </row>
+    <row r="446">
+      <c r="A446" s="6" t="n"/>
+      <c r="C446" s="7" t="n"/>
+      <c r="D446" s="7" t="n"/>
+      <c r="G446" s="8" t="n"/>
+    </row>
+    <row r="447">
+      <c r="A447" s="6" t="n"/>
+      <c r="C447" s="7" t="n"/>
+      <c r="D447" s="7" t="n"/>
+      <c r="G447" s="8" t="n"/>
+    </row>
+    <row r="448">
+      <c r="A448" s="6" t="n"/>
+      <c r="C448" s="7" t="n"/>
+      <c r="D448" s="7" t="n"/>
+      <c r="G448" s="8" t="n"/>
+    </row>
+    <row r="449">
+      <c r="A449" s="6" t="n"/>
+      <c r="C449" s="7" t="n"/>
+      <c r="D449" s="7" t="n"/>
+      <c r="G449" s="8" t="n"/>
+    </row>
+    <row r="450">
+      <c r="A450" s="6" t="n"/>
+      <c r="C450" s="7" t="n"/>
+      <c r="D450" s="7" t="n"/>
+      <c r="G450" s="8" t="n"/>
+    </row>
+    <row r="451">
+      <c r="A451" s="6" t="n"/>
+      <c r="C451" s="7" t="n"/>
+      <c r="D451" s="7" t="n"/>
+      <c r="G451" s="8" t="n"/>
+    </row>
+    <row r="452">
+      <c r="A452" s="6" t="n"/>
+      <c r="C452" s="7" t="n"/>
+      <c r="D452" s="7" t="n"/>
+      <c r="G452" s="8" t="n"/>
+    </row>
+    <row r="453">
+      <c r="A453" s="6" t="n"/>
+      <c r="C453" s="7" t="n"/>
+      <c r="D453" s="7" t="n"/>
+      <c r="G453" s="8" t="n"/>
+    </row>
+    <row r="454">
+      <c r="A454" s="6" t="n"/>
+      <c r="C454" s="7" t="n"/>
+      <c r="D454" s="7" t="n"/>
+      <c r="G454" s="8" t="n"/>
+    </row>
+    <row r="455">
+      <c r="A455" s="6" t="n"/>
+      <c r="C455" s="7" t="n"/>
+      <c r="D455" s="7" t="n"/>
+      <c r="G455" s="8" t="n"/>
+    </row>
+    <row r="456">
+      <c r="A456" s="6" t="n"/>
+      <c r="C456" s="7" t="n"/>
+      <c r="D456" s="7" t="n"/>
+      <c r="G456" s="8" t="n"/>
+    </row>
+    <row r="457">
+      <c r="A457" s="6" t="n"/>
+      <c r="C457" s="7" t="n"/>
+      <c r="D457" s="7" t="n"/>
+      <c r="G457" s="8" t="n"/>
+    </row>
+    <row r="458">
+      <c r="A458" s="6" t="n"/>
+      <c r="C458" s="7" t="n"/>
+      <c r="D458" s="7" t="n"/>
+      <c r="G458" s="8" t="n"/>
+    </row>
+    <row r="459">
+      <c r="A459" s="6" t="n"/>
+      <c r="C459" s="7" t="n"/>
+      <c r="D459" s="7" t="n"/>
+      <c r="G459" s="8" t="n"/>
+    </row>
+    <row r="460">
+      <c r="A460" s="6" t="n"/>
+      <c r="C460" s="7" t="n"/>
+      <c r="D460" s="7" t="n"/>
+      <c r="G460" s="8" t="n"/>
+    </row>
+    <row r="461">
+      <c r="A461" s="6" t="n"/>
+      <c r="C461" s="7" t="n"/>
+      <c r="D461" s="7" t="n"/>
+      <c r="G461" s="8" t="n"/>
+    </row>
+    <row r="462">
+      <c r="A462" s="6" t="n"/>
+      <c r="C462" s="7" t="n"/>
+      <c r="D462" s="7" t="n"/>
+      <c r="G462" s="8" t="n"/>
+    </row>
+    <row r="463">
+      <c r="A463" s="6" t="n"/>
+      <c r="C463" s="7" t="n"/>
+      <c r="D463" s="7" t="n"/>
+      <c r="G463" s="8" t="n"/>
+    </row>
+    <row r="464">
+      <c r="A464" s="6" t="n"/>
+      <c r="C464" s="7" t="n"/>
+      <c r="D464" s="7" t="n"/>
+      <c r="G464" s="8" t="n"/>
+    </row>
+    <row r="465">
+      <c r="A465" s="6" t="n"/>
+      <c r="C465" s="7" t="n"/>
+      <c r="D465" s="7" t="n"/>
+      <c r="G465" s="8" t="n"/>
+    </row>
+    <row r="466">
+      <c r="A466" s="6" t="n"/>
+      <c r="C466" s="7" t="n"/>
+      <c r="D466" s="7" t="n"/>
+      <c r="G466" s="8" t="n"/>
+    </row>
+    <row r="467">
+      <c r="A467" s="6" t="n"/>
+      <c r="C467" s="7" t="n"/>
+      <c r="D467" s="7" t="n"/>
+      <c r="G467" s="8" t="n"/>
+    </row>
+    <row r="468">
+      <c r="A468" s="6" t="n"/>
+      <c r="C468" s="7" t="n"/>
+      <c r="D468" s="7" t="n"/>
+      <c r="G468" s="8" t="n"/>
+    </row>
+    <row r="469">
+      <c r="A469" s="6" t="n"/>
+      <c r="C469" s="7" t="n"/>
+      <c r="D469" s="7" t="n"/>
+      <c r="G469" s="8" t="n"/>
+    </row>
+    <row r="470">
+      <c r="A470" s="6" t="n"/>
+      <c r="C470" s="7" t="n"/>
+      <c r="D470" s="7" t="n"/>
+      <c r="G470" s="8" t="n"/>
+    </row>
+    <row r="471">
+      <c r="A471" s="6" t="n"/>
+      <c r="C471" s="7" t="n"/>
+      <c r="D471" s="7" t="n"/>
+      <c r="G471" s="8" t="n"/>
+    </row>
+    <row r="472">
+      <c r="A472" s="6" t="n"/>
+      <c r="C472" s="7" t="n"/>
+      <c r="D472" s="7" t="n"/>
+      <c r="G472" s="8" t="n"/>
+    </row>
+    <row r="473">
+      <c r="A473" s="6" t="n"/>
+      <c r="C473" s="7" t="n"/>
+      <c r="D473" s="7" t="n"/>
+      <c r="G473" s="8" t="n"/>
+    </row>
+    <row r="474">
+      <c r="A474" s="6" t="n"/>
+      <c r="C474" s="7" t="n"/>
+      <c r="D474" s="7" t="n"/>
+      <c r="G474" s="8" t="n"/>
+    </row>
+    <row r="475">
+      <c r="A475" s="6" t="n"/>
+      <c r="C475" s="7" t="n"/>
+      <c r="D475" s="7" t="n"/>
+      <c r="G475" s="8" t="n"/>
+    </row>
+    <row r="476">
+      <c r="A476" s="6" t="n"/>
+      <c r="C476" s="7" t="n"/>
+      <c r="D476" s="7" t="n"/>
+      <c r="G476" s="8" t="n"/>
+    </row>
+    <row r="477">
+      <c r="A477" s="6" t="n"/>
+      <c r="C477" s="7" t="n"/>
+      <c r="D477" s="7" t="n"/>
+      <c r="G477" s="8" t="n"/>
+    </row>
+    <row r="478">
+      <c r="A478" s="6" t="n"/>
+      <c r="C478" s="7" t="n"/>
+      <c r="D478" s="7" t="n"/>
+      <c r="G478" s="8" t="n"/>
+    </row>
+    <row r="479">
+      <c r="A479" s="6" t="n"/>
+      <c r="C479" s="7" t="n"/>
+      <c r="D479" s="7" t="n"/>
+      <c r="G479" s="8" t="n"/>
+    </row>
+    <row r="480">
+      <c r="A480" s="6" t="n"/>
+      <c r="C480" s="7" t="n"/>
+      <c r="D480" s="7" t="n"/>
+      <c r="G480" s="8" t="n"/>
+    </row>
+    <row r="481">
+      <c r="A481" s="6" t="n"/>
+      <c r="C481" s="7" t="n"/>
+      <c r="D481" s="7" t="n"/>
+      <c r="G481" s="8" t="n"/>
+    </row>
+    <row r="482">
+      <c r="A482" s="6" t="n"/>
+      <c r="C482" s="7" t="n"/>
+      <c r="D482" s="7" t="n"/>
+      <c r="G482" s="8" t="n"/>
+    </row>
+    <row r="483">
+      <c r="A483" s="6" t="n"/>
+      <c r="C483" s="7" t="n"/>
+      <c r="D483" s="7" t="n"/>
+      <c r="G483" s="8" t="n"/>
+    </row>
+    <row r="484">
+      <c r="A484" s="6" t="n"/>
+      <c r="C484" s="7" t="n"/>
+      <c r="D484" s="7" t="n"/>
+      <c r="G484" s="8" t="n"/>
+    </row>
+    <row r="485">
+      <c r="A485" s="6" t="n"/>
+      <c r="C485" s="7" t="n"/>
+      <c r="D485" s="7" t="n"/>
+      <c r="G485" s="8" t="n"/>
+    </row>
+    <row r="486">
+      <c r="A486" s="6" t="n"/>
+      <c r="C486" s="7" t="n"/>
+      <c r="D486" s="7" t="n"/>
+      <c r="G486" s="8" t="n"/>
+    </row>
+    <row r="487">
+      <c r="A487" s="6" t="n"/>
+      <c r="C487" s="7" t="n"/>
+      <c r="D487" s="7" t="n"/>
+      <c r="G487" s="8" t="n"/>
+    </row>
+    <row r="488">
+      <c r="A488" s="6" t="n"/>
+      <c r="C488" s="7" t="n"/>
+      <c r="D488" s="7" t="n"/>
+      <c r="G488" s="8" t="n"/>
+    </row>
+    <row r="489">
+      <c r="A489" s="6" t="n"/>
+      <c r="C489" s="7" t="n"/>
+      <c r="D489" s="7" t="n"/>
+      <c r="G489" s="8" t="n"/>
+    </row>
+    <row r="490">
+      <c r="A490" s="6" t="n"/>
+      <c r="C490" s="7" t="n"/>
+      <c r="D490" s="7" t="n"/>
+      <c r="G490" s="8" t="n"/>
+    </row>
+    <row r="491">
+      <c r="A491" s="6" t="n"/>
+      <c r="C491" s="7" t="n"/>
+      <c r="D491" s="7" t="n"/>
+      <c r="G491" s="8" t="n"/>
+    </row>
+    <row r="492">
+      <c r="A492" s="6" t="n"/>
+      <c r="C492" s="7" t="n"/>
+      <c r="D492" s="7" t="n"/>
+      <c r="G492" s="8" t="n"/>
+    </row>
+    <row r="493">
+      <c r="A493" s="6" t="n"/>
+      <c r="C493" s="7" t="n"/>
+      <c r="D493" s="7" t="n"/>
+      <c r="G493" s="8" t="n"/>
+    </row>
+    <row r="494">
+      <c r="A494" s="6" t="n"/>
+      <c r="C494" s="7" t="n"/>
+      <c r="D494" s="7" t="n"/>
+      <c r="G494" s="8" t="n"/>
+    </row>
+    <row r="495">
+      <c r="A495" s="6" t="n"/>
+      <c r="C495" s="7" t="n"/>
+      <c r="D495" s="7" t="n"/>
+      <c r="G495" s="8" t="n"/>
+    </row>
+    <row r="496">
+      <c r="A496" s="6" t="n"/>
+      <c r="C496" s="7" t="n"/>
+      <c r="D496" s="7" t="n"/>
+      <c r="G496" s="8" t="n"/>
+    </row>
+    <row r="497">
+      <c r="A497" s="6" t="n"/>
+      <c r="C497" s="7" t="n"/>
+      <c r="D497" s="7" t="n"/>
+      <c r="G497" s="8" t="n"/>
+    </row>
+    <row r="498">
+      <c r="A498" s="6" t="n"/>
+      <c r="C498" s="7" t="n"/>
+      <c r="D498" s="7" t="n"/>
+      <c r="G498" s="8" t="n"/>
+    </row>
+    <row r="499">
+      <c r="A499" s="6" t="n"/>
+      <c r="C499" s="7" t="n"/>
+      <c r="D499" s="7" t="n"/>
+      <c r="G499" s="8" t="n"/>
+    </row>
+    <row r="500">
+      <c r="A500" s="6" t="n"/>
+      <c r="C500" s="7" t="n"/>
+      <c r="D500" s="7" t="n"/>
+      <c r="G500" s="8" t="n"/>
+    </row>
   </sheetData>
+  <dataValidations count="3">
+    <dataValidation sqref="B2:B500" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
+      <formula1>"工作日,假期"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E2:E500" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
+      <formula1>"是,否"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F2:F500" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
+      <formula1>"是,否"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>